--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -987,120 +987,10 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>124041834</v>
-      </c>
-      <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Vånga, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>572683</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6381224</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Tuna</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anna Drenk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028121</v>
+        <v>124036675</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R3" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036675</v>
+        <v>124036706</v>
       </c>
       <c r="B4" t="n">
         <v>57507</v>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R4" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +991,121 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124041834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572683</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6381224</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julie Goold</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julie Goold, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124036675</v>
+        <v>124036706</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R2" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124028121</v>
+        <v>124036675</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,40 +789,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -873,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R4" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028121</v>
+        <v>124036675</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124036675</v>
+        <v>124036706</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -826,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R3" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R4" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124036675</v>
+        <v>124028121</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -759,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124036706</v>
+        <v>124036675</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -813,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R3" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,17 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124028121</v>
+        <v>124036706</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,50 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R4" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028121</v>
+        <v>124036706</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R2" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -885,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R4" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R2" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -770,14 +783,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124036675</v>
+        <v>124036706</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -813,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R3" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,17 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124028121</v>
+        <v>124036675</v>
       </c>
       <c r="B4" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,40 +904,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -975,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028121</v>
+        <v>124036675</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Spetsmossen, Sm</t>
@@ -771,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124036706</v>
+        <v>124028121</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R3" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036675</v>
+        <v>124036706</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572757</v>
+        <v>572776</v>
       </c>
       <c r="R4" t="n">
-        <v>6381112</v>
+        <v>6381122</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Julie Goold</t>
+          <t>Julie Goold, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -675,50 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124036675</v>
+        <v>124041834</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spetsmossen, Sm</t>
+          <t>Vånga, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572757</v>
+        <v>572683</v>
       </c>
       <c r="R2" t="n">
-        <v>6381112</v>
+        <v>6381224</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,13 +766,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Julie Goold</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -780,12 +788,7 @@
         <v>124028121</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,19 +895,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124036706</v>
+        <v>124036675</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -928,14 +926,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>tuna_spill2, Sm</t>
+          <t>Spetsmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572776</v>
+        <v>572757</v>
       </c>
       <c r="R4" t="n">
-        <v>6381122</v>
+        <v>6381112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,69 +985,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124041834</v>
+        <v>124036706</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vånga, Sm</t>
+          <t>tuna_spill2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572683</v>
+        <v>572776</v>
       </c>
       <c r="R5" t="n">
-        <v>6381224</v>
+        <v>6381122</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,19 +1071,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Julie Goold</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julie Goold, Anna Drenk</t>
+          <t>Anna Drenk, Julie Goold</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 14584-2025 artfynd.xlsx
+++ b/artfynd/A 14584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028121</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124036675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124036706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124041834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>